--- a/web/src/features/entry/templates/team-entry-template.xlsx
+++ b/web/src/features/entry/templates/team-entry-template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>SN</t>
   </si>
@@ -36,6 +36,9 @@
     <t>Seeding</t>
   </si>
   <si>
+    <t>Manager Email</t>
+  </si>
+  <si>
     <t>Team Entry Template</t>
   </si>
   <si>
@@ -54,6 +57,9 @@
     <t>Club and Seeding are optional.</t>
   </si>
   <si>
+    <t>Manager Email: required — one per team, never used by another team (it becomes the team manager's login in the lineup system).</t>
+  </si>
+  <si>
     <t>Date Of Birth: type a date any way Excel recognizes it (for example 15/01/1990).</t>
   </si>
   <si>
@@ -63,7 +69,7 @@
     <t>SN is numbering only — it is ignored on import.</t>
   </si>
   <si>
-    <t>Column order differs from the Doubles template: SN, Team, Club, Seeding.</t>
+    <t>Column order differs from the Doubles template: SN, Team, Club, Seeding, Manager Email.</t>
   </si>
   <si>
     <t>Example 'players' rows:</t>
@@ -91,6 +97,9 @@
   </si>
   <si>
     <t>Club A</t>
+  </si>
+  <si>
+    <t>manager@cluba.com</t>
   </si>
 </sst>
 </file>
@@ -512,13 +521,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -526,7 +535,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,16 +548,19 @@
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -560,162 +572,173 @@
   <sheetData>
     <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="4">
-        <v>32888</v>
-      </c>
-      <c r="D16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4">
+        <v>32888</v>
+      </c>
+      <c r="D17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="4">
-        <v>33785</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>22</v>
-      </c>
-      <c r="E17" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="4">
+        <v>33785</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="4">
         <v>32450</v>
       </c>
-      <c r="D18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>1</v>
       </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23">
         <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/web/src/features/entry/templates/team-entry-template.xlsx
+++ b/web/src/features/entry/templates/team-entry-template.xlsx
@@ -60,7 +60,7 @@
     <t>Manager Email: required — one per team, never used by another team (it becomes the team manager's login in the lineup system).</t>
   </si>
   <si>
-    <t>Date Of Birth: type a date any way Excel recognizes it (for example 15/01/1990).</t>
+    <t>Date Of Birth: required — type a date any way Excel recognizes it (for example 15/01/1990).</t>
   </si>
   <si>
     <t>Gender: M or F.</t>
